--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Prevenzione.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Prevenzione.xlsx
@@ -85,7 +85,7 @@
     <t>Promemoria appuntamento</t>
   </si>
   <si>
-    <t xml:space="preserve">Erogazione kit per screening </t>
+    <t>Erogazione kit per screening</t>
   </si>
   <si>
     <t>Promemoria consegna campione analisi</t>
@@ -153,7 +153,7 @@
     <t>Utilizza il testo indicato per il pulsante. Inserisci il link alla pagina web che rimanda al servizio.</t>
   </si>
   <si>
-    <t>n/a</t>
+    <t>Scopri di più</t>
   </si>
   <si>
     <t>Link a termini e condizioni d'uso</t>
@@ -445,7 +445,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-L'esame e gli eventuali controlli successivi sono gratuiti. 
+L'esame e gli eventuali controlli successivi sono gratuiti.
 Per ulteriori informazioni sul programma, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -596,7 +596,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-L'esame e gli eventuali controlli successivi sono gratuiti. Ricordati di portare con te questo messaggio e la tessera sanitaria. 
+L'esame e gli eventuali controlli successivi sono gratuiti. Ricordati di portare con te questo messaggio e la tessera sanitaria.
 Per ulteriori informazioni sul programma, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -784,7 +784,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> 
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -838,7 +838,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">.
-L'esame e gli eventuali controlli successivi sono gratuiti. Ricordati di portare con te questo messaggio e la tessera sanitaria. 
+L'esame e gli eventuali controlli successivi sono gratuiti. Ricordati di portare con te questo messaggio e la tessera sanitaria.
 Per ulteriori informazioni sul programma, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -946,7 +946,7 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">.
-L'esame e gli eventuali controlli successivi sono gratuiti. Ricordati di portare con te questo messaggio e la tessera sanitaria. 
+L'esame e gli eventuali controlli successivi sono gratuiti. Ricordati di portare con te questo messaggio e la tessera sanitaria.
 Per ulteriori informazioni sul programma, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -964,10 +964,10 @@
     </r>
   </si>
   <si>
-    <t>Prenota un appuntamento</t>
+    <t>Prenota appuntamento</t>
   </si>
   <si>
-    <t>Gestire prenotazione</t>
+    <t>Gestisci prenotazione</t>
   </si>
   <si>
     <t>-</t>
@@ -990,7 +990,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
